--- a/output/2026-09-03_02_Italia_Campania_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-03_02_Italia_Campania_Impiantistica_aspirazione_industriale.xlsx
@@ -494,10 +494,9 @@
           <t>081 0484254 / 327 6553900 / 334 5499050</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oltre 30 anni di esperienza; canalizzazioni industriali in acciaio inox/lamiera zincata, impianti di aspirazione, filtrazione aria e fumi. Esistenza e attivita confermate via Paginebianche/Europages e sito ufficiale.</t>
+          <t>Oltre 30 anni di esperienza; canalizzazioni industriali in acciaio inox/lamiera zincata, impianti di aspirazione, filtrazione aria e fumi. Esistenza e attivita confermate via Paginebianche/Europages e sito ufficiale. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -581,7 +580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Progettazione/costruzione/installazione di condotti in lamiera zincata/inox per distribuzione aria, canali spiralati per abbattimento fumi/emissioni industriali. Confermato via sito ufficiale e directory.</t>
+          <t>Progettazione/costruzione/installazione di condotti in lamiera zincata/inox per distribuzione aria, canali spiralati per abbattimento fumi/emissioni industriali. Confermato via sito ufficiale e directory. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -616,10 +615,9 @@
           <t>081 5969669</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cappe aspiranti industriali, abbattitori di fuliggine/temperatura, centraline a carboni attivi. Email non confermata in modo univoco (fonti riportano un indirizzo diverso da quello nella lista grezza: mcaimpiantinap@gmail.com); lasciata vuota per assenza di conferma.</t>
+          <t>Cappe aspiranti industriali, abbattitori di fuliggine/temperatura, centraline a carboni attivi. Email non confermata in modo univoco (fonti riportano un indirizzo diverso da quello nella lista grezza: mcaimpiantinap@gmail.com); lasciata vuota per assenza di conferma. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -654,7 +652,6 @@
           <t>347 1894603 / 345 0572874</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Installazione e manutenzione di impianti di aspirazione industriale, impianti a carboni attivi. Confermato tramite sito ufficiale, Facebook e directory di settore.</t>
@@ -699,7 +696,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cappe, canne fumarie, centraline a carboni attivi, abbattitori di fuliggine, impianti di aspirazione fumi (anche per impianti di trattamento pomodoro e aspirazione fumi di saldatura). Copertura su tutta la Campania.</t>
+          <t>Cappe, canne fumarie, centraline a carboni attivi, abbattitori di fuliggine, impianti di aspirazione fumi (anche per impianti di trattamento pomodoro e aspirazione fumi di saldatura). Copertura su tutta la Campania. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -756,7 +753,6 @@
           <t>Gio.Ti.Ca. Impianti di Condizionamento e Aspirazione (di Tiberio Andrea)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Napoli</t>
@@ -772,7 +768,6 @@
           <t>081 5725366</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Ditta individuale specializzata in impianti di condizionamento e aspirazione, confermata su directory (Virgilio, PagineGialle, ReteImprese).</t>
@@ -805,8 +800,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Produzione di cappe industriali e impianti di aspirazione/eliminazione fumi in acciaio inox e lamiera zincata; attivita di famiglia proseguita da circa 50 anni. Telefono/email non verificabili.</t>
@@ -844,10 +837,9 @@
           <t>081 8472396 / 081 8874683</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Progettazione e produzione di impianti di depurazione inquinanti atmosferici, aspirazione e filtrazione aria, depuratori elettrostatici, con certificazione CE. Presenti due domini riconducibili alla stessa azienda (GM/GMA), trattati come unica voce (deduplicata).</t>
+          <t>Progettazione e produzione di impianti di depurazione inquinanti atmosferici, aspirazione e filtrazione aria, depuratori elettrostatici, con certificazione CE. Presenti due domini riconducibili alla stessa azienda (GM/GMA), trattati come unica voce (deduplicata). [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -889,7 +881,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Distributore/rivenditore ufficiale di ventilatori e aspiratori industriali (partner MZ Aspiratori, motori WEG/Simotop), magazzino di 1.200 mq a Fisciano, copertura Sud Italia (Campania, Puglia, Calabria, Sicilia, Sardegna).</t>
+          <t>Distributore/rivenditore ufficiale di ventilatori e aspiratori industriali (partner MZ Aspiratori, motori WEG/Simotop), magazzino di 1.200 mq a Fisciano, copertura Sud Italia (Campania, Puglia, Calabria, Sicilia, Sardegna). [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -924,10 +916,9 @@
           <t>089 7011462 / 089 7012113</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>System integrator: progettazione/fornitura/installazione di impianti di aspirazione e trattamento polveri, filtrazione aria, controllo emissioni industriali; tecnologie proprietarie sviluppate da oltre 40 anni.</t>
+          <t>System integrator: progettazione/fornitura/installazione di impianti di aspirazione e trattamento polveri, filtrazione aria, controllo emissioni industriali; tecnologie proprietarie sviluppate da oltre 40 anni. [DUPLICATO — vedi anche: 2026-09-03_00_Italia_Campania_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -969,7 +960,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Azienda attiva dal 1982, system integrator per aspirazione, ventilazione, filtrazione e climatizzazione industriale/civile, soluzioni personalizzate per diversi settori produttivi.</t>
+          <t>Azienda attiva dal 1982, system integrator per aspirazione, ventilazione, filtrazione e climatizzazione industriale/civile, soluzioni personalizzate per diversi settori produttivi. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1011,7 +1002,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dal 1994, leader nella progettazione/costruzione di impianti di depurazione/aspirazione aria industriale, abbattimento polveri/fumi/solventi, cabine di verniciatura, per settori carta, agroalimentare, tessile, calzaturiero, meccanico, conciario, ceramica/vetro, legno.</t>
+          <t>Dal 1994, leader nella progettazione/costruzione di impianti di depurazione/aspirazione aria industriale, abbattimento polveri/fumi/solventi, cabine di verniciatura, per settori carta, agroalimentare, tessile, calzaturiero, meccanico, conciario, ceramica/vetro, legno. [DUPLICATO — vedi anche: 2026-09-03_00_Italia_Campania_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1046,10 +1037,9 @@
           <t>0825 968300 (numero verde 848 800331)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Produttore di sistemi di aspirapolvere centralizzati e impianti di aspirazione/filtrazione polveri industriali, sede in Contrada Cardogna, Montemiletto (AV). Fonti alternative riportano anche il numero 0825 968573.</t>
+          <t>Produttore di sistemi di aspirapolvere centralizzati e impianti di aspirazione/filtrazione polveri industriali, sede in Contrada Cardogna, Montemiletto (AV). Fonti alternative riportano anche il numero 0825 968573. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1121,8 +1111,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Progettazione e produzione di impianti di aspirazione e abbattimento di fumi, polveri e odori, ventilazione e impianti aria compressa; macchine progettate e prodotte interamente in Italia. Telefono/email non verificabili dai risultati di ricerca.</t>
@@ -1140,7 +1128,6 @@
           <t>Q TEC S.R.L.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Caserta</t>
@@ -1156,7 +1143,6 @@
           <t>0823354655</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Azienda fondata nel 1996, specializzata in impianti di aspirazione di fumo industriale. Presenza confermata su Europages; sito web proprio non individuato/verificabile.</t>
@@ -1201,7 +1187,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Vendita e assistenza di compressori, essiccatori, idropulitrici e aspiratori industriali; opera su Caserta, Napoli, Avellino, Benevento.</t>
+          <t>Vendita e assistenza di compressori, essiccatori, idropulitrici e aspiratori industriali; opera su Caserta, Napoli, Avellino, Benevento. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1236,10 +1222,9 @@
           <t>081 4617528</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cappe aspiranti, centraline a carboni attivi, abbattitori di fuliggine, canne fumarie; anche impianti di aspirazione fumi di saldatura per carrozzerie e trattamento aria per stabilimenti di pomodoro. Oltre 20 anni di esperienza, copertura regionale Campania.</t>
+          <t>Cappe aspiranti, centraline a carboni attivi, abbattitori di fuliggine, canne fumarie; anche impianti di aspirazione fumi di saldatura per carrozzerie e trattamento aria per stabilimenti di pomodoro. Oltre 20 anni di esperienza, copertura regionale Campania. [DUPLICATO — vedi anche: 2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
